--- a/artfynd/A 22889-2026 artfynd.xlsx
+++ b/artfynd/A 22889-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119544375</v>
+        <v>119544470</v>
       </c>
       <c r="B2" t="n">
-        <v>56962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102966</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561748</v>
+        <v>561755</v>
       </c>
       <c r="R2" t="n">
-        <v>6730615</v>
+        <v>6730740</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gammal blåbärstallskog</t>
+          <t>äldre blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119544404</v>
+        <v>130962270</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+          <t>Toxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561822</v>
+        <v>561779</v>
       </c>
       <c r="R3" t="n">
-        <v>6730634</v>
+        <v>6730629</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,17 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,36 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal lingontallskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130962269</v>
+        <v>119544409</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Toxberget, Dlr</t>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561840</v>
+        <v>561822</v>
       </c>
       <c r="R4" t="n">
-        <v>6730629</v>
+        <v>6730610</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,19 +975,1104 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gammal blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130962293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>561775</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6730618</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Alfred Olofsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119544401</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561774</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6730630</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>gammal lingontallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119544404</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561822</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6730634</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>gammal lingontallskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130962269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561840</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6730629</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130962292</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561785</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6730631</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119544375</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57563</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>561748</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6730615</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>gammal blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119544407</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>561821</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6730617</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>gammal blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119544412</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>561878</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6730616</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre blåbärsbarrblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119544472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>St. Skogsbotjärnen, skog i anslutning., Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>561753</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6730740</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kopparfors Skogar naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130962375</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Toxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>561672</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6730600</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Sofia Damne, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22889-2026 artfynd.xlsx
+++ b/artfynd/A 22889-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544409</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962293</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544401</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962292</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544375</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544407</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544412</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544472</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,8 +2138,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962375</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>